--- a/vault-dalarna-university/02 IHV/Analys/Betygsrapportering.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Betygsrapportering.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Betygsrapportering" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Betygsrapportering'!$A$1:$E$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Betygsrapportering'!$A$1:$E$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1738,8 +1738,116 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>FHV0001</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. Betygsrapportering: Moment 1: Vetenskaps- och kunskapsteori 2,5 hp Moment 2: Forskningsetik…</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>FHV0002</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. För betyget godkänd på kursen krävs Godkänt på alla momenten.…</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>FHV0003</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. För betyget godkänd på kursen krävs Godkänt på alla momenten…</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>FVV222H</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. För betyget godkänd på kursen krävs Godkänt på alla momenten listade nedan. Betygsrapporter…</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FVV222H</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E48"/>
+  <autoFilter ref="A1:E52"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1835,6 +1943,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Betygsrapportering.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Betygsrapportering.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Betygsrapportering" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Betygsrapportering'!$A$1:$E$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Betygsrapportering'!$A$1:$G$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att få betyget VG på hela kursen, krävs VG på modul 1 och 3, samt G på modul 2. Betygs…</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2022-02-28</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Muntlig redovisning och skriftliga inlämningsuppgifter - 7,5 …</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Muntlig redovisning och skriftliga inlämningsuppgifter - 7,5 …</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För betyget väl godkänd på hela kursen krävs väl godkänd på minst tre av delkurserna.…</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
         </is>
@@ -590,15 +626,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För väl godkänd på hela kursen krävs väl godkänd på minst tre av delkurserna.…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
@@ -617,15 +659,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att erhålla betyget väl godkänd på hela kursen krävs väl godkänd på delkurs 2 samt på …</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
         </is>
@@ -644,15 +692,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att erhålla betyget väl godkänd på hela kursen krävs väl godkänd på båda delkurserna.…</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
         </is>
@@ -671,15 +725,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
         </is>
@@ -698,15 +758,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
         </is>
@@ -725,15 +791,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
         </is>
@@ -752,15 +824,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
         </is>
@@ -779,15 +857,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
         </is>
@@ -806,15 +890,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
         </is>
@@ -833,15 +923,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
@@ -860,15 +956,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
         </is>
@@ -887,15 +989,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
         </is>
@@ -914,15 +1026,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
         </is>
@@ -941,15 +1063,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
         </is>
@@ -968,15 +1100,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
         </is>
@@ -995,15 +1137,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
         </is>
@@ -1022,15 +1174,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
         </is>
@@ -1049,15 +1211,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2011-03-30</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För väl godkänd på hela kusen krävs väl godkänd på minst 22,5 högskolepoäng.…</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
         </is>
@@ -1076,15 +1244,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2012-12-05</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2013-11-25</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För att erhålla betyget VG på hela kursen krävs betyget VG i minst tre av delkurserna.…</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
         </is>
@@ -1103,15 +1281,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För väl godkänd på hela kursen krävs väl godkänd på delkurs 3 samt väl godkänd på minst en…</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
@@ -1130,15 +1314,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. För väl godkänd på hela kursen krävs väl godkänd på minst tre av delkurserna.…</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
@@ -1157,15 +1347,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
         </is>
@@ -1184,15 +1380,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
         </is>
@@ -1211,15 +1413,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
         </is>
@@ -1238,15 +1446,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
         </is>
@@ -1265,15 +1479,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>2014-02-12</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
         </is>
@@ -1292,15 +1516,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2013-03-15</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>2014-02-12</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används A–F.…</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
         </is>
@@ -1319,15 +1553,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
@@ -1346,15 +1586,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
@@ -1373,15 +1619,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsmoduler:…</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
@@ -1400,15 +1652,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Seminarier, inlämningsuppgifter, skriftlig tentamen - 7,5 hp…</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
         </is>
@@ -1427,15 +1685,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2021-12-08</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Seminarier, skriftliga inlämningsuppgifter, hemtentamen - 7,5…</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
         </is>
@@ -1454,15 +1718,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+          <t>2021-12-08</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betygsrapportering: Modul 1: Seminarier, skriftliga inlämningsuppgifter, hemtentamen - 7,5…</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
@@ -1481,15 +1751,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2009-04-21</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>2012-03-05</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
         </is>
@@ -1508,15 +1788,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>2012-03-05</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
@@ -1535,15 +1825,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2008-03-03</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
         </is>
@@ -1562,15 +1858,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2008-03-03</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>2015-10-02</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
         </is>
@@ -1589,15 +1895,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2009-04-21</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>2010-10-18</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
         </is>
@@ -1616,15 +1932,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2009-04-21</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>2010-10-18</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
         </is>
@@ -1643,15 +1969,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2009-05-26</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>2012-01-26</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
         </is>
@@ -1670,15 +2006,25 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2009-12-14</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>2013-08-26</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G.…</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
         </is>
@@ -1697,15 +2043,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2010-06-01</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>2010-10-18</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG.…</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
@@ -1724,15 +2080,25 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2012-01-12</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>2018-11-14</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–VG. Betyg rapporteras som Examensarbete, 15 hp…</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
@@ -1751,15 +2117,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>2018-01-25</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. Betygsrapportering: Moment 1: Vetenskaps- och kunskapsteori 2,5 hp Moment 2: Forskningsetik…</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
         </is>
@@ -1778,15 +2150,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2018-03-28</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. För betyget godkänd på kursen krävs Godkänt på alla momenten.…</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0002</t>
         </is>
@@ -1805,15 +2187,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. För betyget godkänd på kursen krävs Godkänt på alla momenten…</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0003</t>
         </is>
@@ -1832,125 +2220,135 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Saknar punktlista</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>2023-01-19</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Saknar punktlista</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>Betyg skrivet utan punktlista: Som betygsskala används U–G. För betyget godkänd på kursen krävs Godkänt på alla momenten listade nedan. Betygsrapporter…</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FVV222H</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E52"/>
+  <autoFilter ref="A1:G52"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
